--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="545">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1064,6 +1064,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>obs-7
 obs-6</t>
   </si>
@@ -1117,6 +1120,102 @@
 obs-6obs-nihss-code</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRange</t>
+  </si>
+  <si>
+    <t>valueRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRatio</t>
+  </si>
+  <si>
+    <t>valueRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueSampledData</t>
+  </si>
+  <si>
+    <t>valueSampledData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SampledData
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueTime</t>
+  </si>
+  <si>
+    <t>valueTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valuePeriod</t>
+  </si>
+  <si>
+    <t>valuePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueAttachment</t>
+  </si>
+  <si>
+    <t>valueAttachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueReference</t>
+  </si>
+  <si>
+    <t>valueReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(MolecularSequence|5.0.0)
+</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1400,6 +1499,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -1490,10 +1593,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
   </si>
   <si>
     <t>Applicable age range, if relevant</t>
@@ -1974,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
@@ -5830,7 +5929,7 @@
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>144</v>
+        <v>329</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>322</v>
@@ -5842,7 +5941,7 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
@@ -5854,27 +5953,27 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>322</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
@@ -5896,7 +5995,7 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>324</v>
@@ -5966,7 +6065,7 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
@@ -5978,27 +6077,27 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>322</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>20</v>
@@ -6061,7 +6160,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -6088,7 +6187,7 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6100,27 +6199,27 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>322</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
@@ -6142,7 +6241,7 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>324</v>
@@ -6212,7 +6311,7 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6224,26 +6323,28 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6261,22 +6362,22 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6301,13 +6402,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6325,7 +6426,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6334,7 +6435,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6346,35 +6447,37 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="D37" t="s" s="2">
-        <v>356</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6383,22 +6486,22 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>243</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6423,13 +6526,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6447,16 +6550,16 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6468,26 +6571,28 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>366</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6496,7 +6601,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6505,22 +6610,22 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6569,16 +6674,16 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6590,26 +6695,28 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>374</v>
+        <v>333</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6627,21 +6734,23 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6665,13 +6774,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6689,7 +6798,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>375</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6698,7 +6807,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>382</v>
+        <v>330</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6710,26 +6819,28 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>383</v>
+        <v>331</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>386</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6747,21 +6858,23 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>389</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6809,7 +6922,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>387</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6818,7 +6931,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>382</v>
+        <v>330</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6830,26 +6943,28 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6867,22 +6982,22 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>243</v>
+        <v>362</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>395</v>
+        <v>326</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6907,13 +7022,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>398</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6931,7 +7046,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6940,7 +7055,7 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>105</v>
@@ -6952,26 +7067,28 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>399</v>
+        <v>332</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>400</v>
+        <v>333</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6989,21 +7106,23 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>325</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -7051,7 +7170,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7060,10 +7179,10 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>406</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -7072,26 +7191,28 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>409</v>
+        <v>333</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>410</v>
+        <v>334</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7109,21 +7230,23 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>324</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>325</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7171,7 +7294,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7180,7 +7303,7 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>105</v>
@@ -7192,26 +7315,28 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>331</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>332</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>418</v>
+        <v>333</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7220,7 +7345,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7229,22 +7354,22 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>186</v>
+        <v>371</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>324</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>325</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>423</v>
+        <v>326</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>424</v>
+        <v>327</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7293,19 +7418,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>322</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>425</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7314,26 +7439,28 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>426</v>
+        <v>332</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>427</v>
+        <v>333</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7351,19 +7478,23 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>190</v>
+        <v>374</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>191</v>
+        <v>324</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7411,7 +7542,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7420,10 +7551,10 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7432,35 +7563,35 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>195</v>
+        <v>333</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>375</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7472,18 +7603,20 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>197</v>
+        <v>376</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>198</v>
+        <v>377</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7507,13 +7640,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7531,19 +7664,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>199</v>
+        <v>375</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7555,10 +7688,10 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>195</v>
+        <v>384</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>20</v>
@@ -7566,14 +7699,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>201</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7586,25 +7719,25 @@
         <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>202</v>
+        <v>387</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>203</v>
+        <v>388</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>157</v>
+        <v>389</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>158</v>
+        <v>390</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7629,13 +7762,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7653,7 +7786,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>204</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7665,7 +7798,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7674,24 +7807,24 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>138</v>
+        <v>395</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7702,7 +7835,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7714,16 +7847,20 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7771,16 +7908,16 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>435</v>
+        <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7795,10 +7932,10 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -7806,10 +7943,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7832,15 +7969,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>432</v>
+        <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7865,13 +8004,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7889,7 +8028,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7898,7 +8037,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7910,24 +8049,24 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7950,15 +8089,17 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>418</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7983,13 +8124,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -8007,7 +8148,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8016,7 +8157,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8031,10 +8172,10 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -8042,10 +8183,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8071,16 +8212,16 @@
         <v>243</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8105,13 +8246,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>249</v>
+        <v>409</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8129,7 +8270,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8150,13 +8291,13 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>454</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>365</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8164,10 +8305,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8178,7 +8319,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8190,20 +8331,18 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>243</v>
+        <v>432</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8227,13 +8366,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>461</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>462</v>
+        <v>20</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8251,19 +8390,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>436</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8272,24 +8411,24 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>365</v>
+        <v>439</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>20</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8312,18 +8451,18 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8371,7 +8510,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8392,24 +8531,24 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>20</v>
+        <v>446</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>20</v>
+        <v>449</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8420,7 +8559,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8432,16 +8571,20 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>470</v>
+        <v>186</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8489,19 +8632,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>435</v>
+        <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>455</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8513,10 +8656,10 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>20</v>
@@ -8524,10 +8667,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8538,7 +8681,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8547,20 +8690,18 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>475</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>476</v>
+        <v>191</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8609,19 +8750,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8633,10 +8774,10 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>20</v>
@@ -8644,14 +8785,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8667,19 +8808,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>481</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>482</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>483</v>
+        <v>198</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>484</v>
+        <v>157</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8729,7 +8870,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8741,7 +8882,7 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8753,10 +8894,10 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>485</v>
+        <v>195</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>20</v>
@@ -8764,14 +8905,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8784,25 +8925,25 @@
         <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>487</v>
+        <v>202</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>488</v>
+        <v>203</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>489</v>
+        <v>157</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>490</v>
+        <v>158</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8851,7 +8992,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>486</v>
+        <v>204</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8860,10 +9001,10 @@
         <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8875,10 +9016,10 @@
         <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>491</v>
+        <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>492</v>
+        <v>138</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -8886,10 +9027,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8912,13 +9053,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>190</v>
+        <v>462</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>191</v>
+        <v>463</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>192</v>
+        <v>464</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8969,7 +9110,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>193</v>
+        <v>461</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8978,10 +9119,10 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>194</v>
+        <v>465</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>20</v>
+        <v>466</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8993,10 +9134,10 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>195</v>
+        <v>467</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9004,21 +9145,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9030,17 +9171,15 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>462</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>197</v>
+        <v>469</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9089,19 +9228,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>199</v>
+        <v>468</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>20</v>
+        <v>465</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>466</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9113,10 +9252,10 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>195</v>
+        <v>471</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9124,46 +9263,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>202</v>
+        <v>473</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -9187,13 +9322,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>20</v>
+        <v>476</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9211,19 +9346,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>204</v>
+        <v>472</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9235,10 +9370,10 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>138</v>
+        <v>477</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>20</v>
@@ -9246,10 +9381,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9257,7 +9392,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>93</v>
@@ -9269,22 +9404,22 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>259</v>
+        <v>482</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9309,13 +9444,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>379</v>
+        <v>249</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9333,16 +9468,16 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9351,16 +9486,16 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>265</v>
+        <v>486</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>20</v>
@@ -9368,10 +9503,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9382,7 +9517,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9391,22 +9526,22 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>323</v>
+        <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>325</v>
+        <v>489</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>327</v>
+        <v>491</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9431,13 +9566,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>20</v>
+        <v>492</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9455,13 +9590,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9476,24 +9611,24 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>331</v>
+        <v>486</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9516,19 +9651,17 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>243</v>
+        <v>353</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>349</v>
+        <v>497</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9553,13 +9686,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9577,7 +9710,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9601,10 +9734,10 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>354</v>
+        <v>498</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>20</v>
@@ -9612,21 +9745,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>356</v>
+        <v>20</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9638,20 +9771,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>243</v>
+        <v>500</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>501</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9675,13 +9804,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9699,16 +9828,16 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>20</v>
+        <v>465</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -9720,24 +9849,24 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>364</v>
+        <v>456</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>365</v>
+        <v>503</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9757,23 +9886,21 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -9821,7 +9948,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9845,17 +9972,1229 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>426</v>
+        <v>509</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>427</v>
+        <v>209</v>
       </c>
       <c r="AP65" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP65">
+  <autoFilter ref="A1:AP75">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9865,7 +11204,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-functional-score-observation-profile.xlsx
+++ b/StructureDefinition-functional-score-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
